--- a/branches/docs/upstream-genomics-reporting/observations-summary.xlsx
+++ b/branches/docs/upstream-genomics-reporting/observations-summary.xlsx
@@ -143,7 +143,7 @@
     <t>mii-pr-molgen-molekularer-biomarker</t>
   </si>
   <si>
-    <t>MII PR MolGen Molekulare Biomarker</t>
+    <t>MII PR MolGen Molekularer Biomarker</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory, To Be Determined Codes#biomarker-category, diagnosticServiceSectionId#GE</t>
